--- a/r5-core-main/StructureDefinition-at-core-location.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-location.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="392">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-location</t>
+    <t>https://fhir.hl7.at/core/r5/StructureDefinition/at-core-location</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T05:18:04+00:00</t>
+    <t>2026-10-13T05:41:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -976,7 +976,7 @@
     <t>Location.contact</t>
   </si>
   <si>
-    <t xml:space="preserve">ExtendedContactDetail {http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-extendedContactDetail}
+    <t xml:space="preserve">ExtendedContactDetail {https://fhir.hl7.at/core/r5/StructureDefinition/at-core-extendedContactDetail}
 </t>
   </si>
   <si>
@@ -999,7 +999,7 @@
     <t>Location.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-address}
+    <t xml:space="preserve">Address {https://fhir.hl7.at/core/r5/StructureDefinition/at-core-address}
 </t>
   </si>
   <si>
@@ -1013,6 +1013,10 @@
   </si>
   <si>
     <t>If locations can be visited, we need to keep track of their address.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+at-addr-1:If the extension for street name is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-streetName').empty() or $this.hasValue())}at-addr-2:If the extension for street number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-houseNumber').empty() or $this.hasValue())}at-addr-3:If the extension for floor/door number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-additionalLocator').empty() or $this.hasValue())}</t>
   </si>
   <si>
     <t>.addr</t>
@@ -1127,7 +1131,7 @@
     <t>Location.managingOrganization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-organization)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/core/r5/StructureDefinition/at-core-organization)
 </t>
   </si>
   <si>
@@ -1149,7 +1153,7 @@
     <t>Location.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-location)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/core/r5/StructureDefinition/at-core-location)
 </t>
   </si>
   <si>
@@ -1566,7 +1570,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="94.0390625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="81.37890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -5477,24 +5481,24 @@
         <v>21</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>320</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5520,14 +5524,14 @@
         <v>184</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -5552,13 +5556,13 @@
         <v>21</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>21</v>
@@ -5576,7 +5580,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5594,7 +5598,7 @@
         <v>300</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
@@ -5602,10 +5606,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5628,19 +5632,19 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -5689,7 +5693,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5707,7 +5711,7 @@
         <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>21</v>
@@ -5715,10 +5719,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5824,10 +5828,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5935,14 +5939,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -5964,10 +5968,10 @@
         <v>135</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>138</v>
@@ -6022,7 +6026,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6048,10 +6052,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6074,13 +6078,13 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6131,7 +6135,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>87</v>
@@ -6149,7 +6153,7 @@
         <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>21</v>
@@ -6157,10 +6161,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6183,13 +6187,13 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6240,7 +6244,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>87</v>
@@ -6258,7 +6262,7 @@
         <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
@@ -6266,10 +6270,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6292,13 +6296,13 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6349,7 +6353,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6367,7 +6371,7 @@
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
@@ -6375,10 +6379,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6401,19 +6405,19 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -6462,7 +6466,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6480,7 +6484,7 @@
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
@@ -6488,10 +6492,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6514,17 +6518,17 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -6573,7 +6577,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6591,7 +6595,7 @@
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
@@ -6599,10 +6603,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6628,13 +6632,13 @@
         <v>184</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6660,13 +6664,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -6684,7 +6688,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6702,7 +6706,7 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
@@ -6710,10 +6714,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6736,16 +6740,16 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6795,7 +6799,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6813,7 +6817,7 @@
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>21</v>
@@ -6821,10 +6825,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6847,16 +6851,16 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6906,7 +6910,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6932,10 +6936,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6958,17 +6962,17 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>21</v>
@@ -7017,7 +7021,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>

--- a/r5-core-main/StructureDefinition-at-core-location.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T05:41:37+00:00</t>
+    <t>2026-10-16T04:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
